--- a/quantitativos/Quantitativo_Armaduras_DE-5400.00-6310-120-TX3-002.xlsx
+++ b/quantitativos/Quantitativo_Armaduras_DE-5400.00-6310-120-TX3-002.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Lista de Barras" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Resumo por Bitola" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Resumo por Posição" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Quantitativo por Tanque" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Quantitativo Unitário" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Geometria e Seções" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Parâmetros Técnicos" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Validações" sheetId="8" state="visible" r:id="rId8"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Lista de Barras'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Resumo por Bitola'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Resumo por Posição'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Quantitativo por Tanque'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Quantitativo Unitário'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Geometria e Seções'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Parâmetros Técnicos'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Validações'!$1:$5</definedName>
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -216,10 +216,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -279,9 +279,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1076,7 +1073,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PAINEL DE QUANTITATIVOS - ARMADURAS DAS FUNDAÇÕES DOS TANQUES DE LUBRIFICAÇÃO</t>
+          <t>PAINEL DE QUANTITATIVOS - ARMADURAS DAS FUNDAÇÕES DOS TQ-6310816/817 A/B/C/D</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1163,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>tanques idênticos cobertos pela prancha</t>
+          <t>tanques cobertos pela prancha</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>posições N1 a N13 na lista de barras</t>
+          <t>posições N1 a N13 na lista</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1246,12 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Ø8, Ø16 e Ø20 mm - aço CA-50</t>
+          <t>bitolas distintas — aço CA-50</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>un (N8 + N9 + N12) nas 8 fundações</t>
+          <t>un de estribo no conjunto</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
@@ -1269,57 +1266,57 @@
           <t>COMPOSIÇÃO POR BITOLA</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
       <c r="H15" s="11" t="inlineStr">
         <is>
           <t>PARTICIPAÇÃO POR FUNÇÃO ESTRUTURAL</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Bitola</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Compr. total (m)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Massa (kg)</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>% da massa</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Barras 12 m</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>Função estrutural</t>
         </is>
       </c>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>Massa (kg)</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>% da massa</t>
         </is>
@@ -1455,7 +1452,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I21" s="13" t="n"/>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="21" t="n">
         <v>30598.9</v>
       </c>
@@ -1466,22 +1463,22 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>MASSA POR POSIÇÃO DE BARRA (N1 A N13) - FONTE: ABA RESUMO POR POSIÇÃO</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
+          <t>MASSA POR POSIÇÃO DE BARRA - FONTE: ABA RESUMO POR POSIÇÃO</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="12" t="n"/>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="12" t="n"/>
+      <c r="N40" s="12" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -1489,59 +1486,59 @@
           <t>CONTROLE DE VALIDAÇÃO - DESTAQUES</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n"/>
+      <c r="N60" s="12" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Calculado</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Referência</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>Desvio</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
         <is>
           <t>Critério</t>
         </is>
       </c>
-      <c r="H61" s="13" t="n"/>
-      <c r="I61" s="13" t="n"/>
-      <c r="J61" s="13" t="n"/>
-      <c r="K61" s="13" t="n"/>
-      <c r="L61" s="13" t="n"/>
-      <c r="M61" s="13" t="n"/>
-      <c r="N61" s="13" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="12" t="n"/>
+      <c r="N61" s="12" t="n"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
@@ -1600,7 +1597,7 @@
       </c>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>Diferença de arredondamento do TOTAL (kg) impresso.</t>
+          <t>Diferença apenas de arredondamento do TOTAL (kg) impresso.</t>
         </is>
       </c>
       <c r="H63" s="19" t="n"/>
@@ -1612,38 +1609,38 @@
       <c r="N63" s="19" t="n"/>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>Multiplicidade 8x</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>N8 - 298 c/20 por fundação x 8</t>
-        </is>
-      </c>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="27" t="n">
-        <v>2384</v>
-      </c>
-      <c r="E64" s="27" t="n">
-        <v>2384</v>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="26" t="inlineStr">
-        <is>
-          <t>Confirma que as colunas QUANT. e TOTAL da lista já são o conjunto das 8 fundações.</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="n"/>
-      <c r="I64" s="19" t="n"/>
-      <c r="J64" s="19" t="n"/>
-      <c r="K64" s="19" t="n"/>
-      <c r="L64" s="19" t="n"/>
-      <c r="M64" s="19" t="n"/>
-      <c r="N64" s="19" t="n"/>
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>DIVERGÊNCIA</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>N13 - quantidade por fundação (un)</t>
+        </is>
+      </c>
+      <c r="C64" s="30" t="n"/>
+      <c r="D64" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G64" s="29" t="inlineStr">
+        <is>
+          <t>Lista traz 8 un (1/fundação); o detalhe chama 'N13-2' (2/fundação), leitura reforçada pela prancha irmã TX3-060. Se prevalecer: +8 un, +38,80 m, +61,23 kg. Confirmar.</t>
+        </is>
+      </c>
+      <c r="H64" s="30" t="n"/>
+      <c r="I64" s="30" t="n"/>
+      <c r="J64" s="30" t="n"/>
+      <c r="K64" s="30" t="n"/>
+      <c r="L64" s="30" t="n"/>
+      <c r="M64" s="30" t="n"/>
+      <c r="N64" s="30" t="n"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="28" t="inlineStr">
@@ -1653,22 +1650,22 @@
       </c>
       <c r="B65" s="29" t="inlineStr">
         <is>
-          <t>N13 - quantidade por fundação (un)</t>
+          <t>N12 - comprimento unitário implícito (m)</t>
         </is>
       </c>
       <c r="C65" s="30" t="n"/>
       <c r="D65" s="31" t="n">
-        <v>1</v>
+        <v>4.71</v>
       </c>
       <c r="E65" s="31" t="n">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="F65" s="31" t="n">
-        <v>-1</v>
+        <v>3.48</v>
       </c>
       <c r="G65" s="29" t="inlineStr">
         <is>
-          <t>Lista traz 8 un (1/fundação); o detalhe chama 'N13-2' (2/fundação). Se prevalecer o detalhe: +8 un, +38,80 m, +61,23 kg. Confirmar.</t>
+          <t>Forma cotada como (113 a 133) cm, mas o TOTAL de 150,72 m para 32 un implica 471 cm por barra. Confirmar.</t>
         </is>
       </c>
       <c r="H65" s="30" t="n"/>
@@ -1687,22 +1684,22 @@
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>N12 - comprimento unitário implícito (m)</t>
+          <t>Cotas FACE INTERNA vs. FACE SUP./INF. (m)</t>
         </is>
       </c>
       <c r="C66" s="30" t="n"/>
       <c r="D66" s="31" t="n">
-        <v>4.71</v>
+        <v>59.942</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>1.23</v>
+        <v>58.327</v>
       </c>
       <c r="F66" s="31" t="n">
-        <v>3.48</v>
+        <v>1.615</v>
       </c>
       <c r="G66" s="29" t="inlineStr">
         <is>
-          <t>Forma cotada como (113 a 133) cm, mas o TOTAL de 150,72 m para 32 un implica 471 cm por barra. Confirmar.</t>
+          <t>A média de externa e interna tem de dar o eixo: (61,556+58,327)/2 = 59,942, valor impresso na FACE INTERNA. Os dois desenvolvimentos parecem trocados entre as vistas. Não afeta o aço.</t>
         </is>
       </c>
       <c r="H66" s="30" t="n"/>
@@ -1714,7 +1711,7 @@
       <c r="N66" s="30" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="48">
     <mergeCell ref="A40:N40"/>
     <mergeCell ref="A10:C11"/>
     <mergeCell ref="B62:C62"/>
@@ -1722,7 +1719,6 @@
     <mergeCell ref="D5:F6"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="D10:F11"/>
-    <mergeCell ref="A20"/>
     <mergeCell ref="J5:L6"/>
     <mergeCell ref="A60:N60"/>
     <mergeCell ref="B66:C66"/>
@@ -1819,81 +1815,81 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>POS.</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Elemento</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Bitola
 Ø (mm)</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Quant. total
 (8 fundações)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Compr. unit.
 (cm)</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Compr. total
 (m) - 8x</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Massa linear
 (kg/m)</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Massa total
 (kg) - 8x</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>% da massa</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>Quant. por
 fundação</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>Compr. por
 fundação (m)</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Massa por
 fundação (kg)</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>Função estrutural</t>
         </is>
       </c>
-      <c r="N5" s="12" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>Vista de referência</t>
         </is>
@@ -1908,7 +1904,7 @@
           <t>N1</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="14" t="n">
         <v>20</v>
       </c>
       <c r="D6" s="17" t="n">
@@ -1960,7 +1956,7 @@
           <t>N2</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="14" t="n">
         <v>20</v>
       </c>
       <c r="D7" s="17" t="n">
@@ -2012,7 +2008,7 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="14" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="17" t="n">
@@ -2064,7 +2060,7 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="14" t="n">
         <v>20</v>
       </c>
       <c r="D9" s="17" t="n">
@@ -2116,7 +2112,7 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="14" t="n">
         <v>20</v>
       </c>
       <c r="D10" s="17" t="n">
@@ -2168,7 +2164,7 @@
           <t>N6</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="14" t="n">
         <v>16</v>
       </c>
       <c r="D11" s="17" t="n">
@@ -2220,7 +2216,7 @@
           <t>N7</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="14" t="n">
         <v>16</v>
       </c>
       <c r="D12" s="17" t="n">
@@ -2272,14 +2268,16 @@
           <t>N8</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="14" t="n">
         <v>8</v>
       </c>
       <c r="D13" s="17" t="n">
         <v>2384</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>465</v>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
       </c>
       <c r="F13" s="15" t="n">
         <v>11085.6</v>
@@ -2322,14 +2320,16 @@
           <t>N9</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="14" t="n">
         <v>8</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <v>473</v>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
       </c>
       <c r="F14" s="15" t="n">
         <v>227.04</v>
@@ -2372,14 +2372,16 @@
           <t>N10</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="14" t="n">
         <v>16</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="E15" s="14" t="n">
-        <v>500</v>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="F15" s="15" t="n">
         <v>160</v>
@@ -2422,14 +2424,16 @@
           <t>N11</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="14" t="n">
         <v>20</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>600</v>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="F16" s="15" t="n">
         <v>192</v>
@@ -2472,7 +2476,7 @@
           <t>N12</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="14" t="n">
         <v>8</v>
       </c>
       <c r="D17" s="17" t="n">
@@ -2524,14 +2528,16 @@
           <t>N13</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="14" t="n">
         <v>16</v>
       </c>
       <c r="D18" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E18" s="14" t="n">
-        <v>485</v>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
       </c>
       <c r="F18" s="15" t="n">
         <v>38.8</v>
@@ -2571,7 +2577,7 @@
           <t>TOTAL — 13 posições</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
+      <c r="B19" s="12" t="n"/>
       <c r="C19" s="20" t="n"/>
       <c r="D19" s="23" t="n">
         <v>2712</v>
@@ -2612,7 +2618,7 @@
       </c>
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>Barra corrida (CORR) do banzo superior e inferior; 2 un por fundação (1 sup. + 1 inf.).</t>
+          <t>Barra corrida (CORR) do banzo superior e inferior. 2 un por fundação (1 sup. + 1 inf.); 71,40 m de desenvolvimento por barra.</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2630,7 @@
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>Barra corrida (CORR) do banzo superior e inferior; 2 un por fundação (1 sup. + 1 inf.).</t>
+          <t>Barra corrida (CORR) do banzo superior e inferior. 2 un por fundação (1 sup. + 1 inf.); 75,40 m de desenvolvimento por barra.</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2642,7 @@
       </c>
       <c r="B24" s="32" t="inlineStr">
         <is>
-          <t>Barra corrida (CORR) do banzo superior e inferior; 2 un por fundação (1 sup. + 1 inf.).</t>
+          <t>Barra corrida (CORR) do banzo superior e inferior. 2 un por fundação (1 sup. + 1 inf.); 75,40 m de desenvolvimento por barra.</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2654,7 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>Barra corrida (CORR) do banzo superior e inferior; 2 un por fundação (1 sup. + 1 inf.).</t>
+          <t>Barra corrida (CORR) do banzo superior e inferior. 2 un por fundação (1 sup. + 1 inf.); 75,40 m de desenvolvimento por barra.</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2666,7 @@
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>Barra corrida (CORR) do banzo superior e inferior; 2 un por fundação (1 sup. + 1 inf.).</t>
+          <t>Barra corrida (CORR) do banzo superior e inferior. 2 un por fundação (1 sup. + 1 inf.); 75,60 m de desenvolvimento por barra.</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2678,7 @@
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t>6 N6 c/20 na face externa; barra corrida (CORR) ao longo do desenvolvimento do anel.</t>
+          <t>6 N6 c/20 na face externa (5 N6 c/20 no trecho do rebaixo, CORTE B-B); barra corrida ao longo do desenvolvimento do anel.</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2690,7 @@
       </c>
       <c r="B28" s="32" t="inlineStr">
         <is>
-          <t>6 N7 c/20 na face interna; barra corrida (CORR) ao longo do desenvolvimento do anel.</t>
+          <t>6 N7 c/20 na face interna (5 N7 c/20 no trecho do rebaixo, CORTE B-B); barra corrida ao longo do desenvolvimento do anel.</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2702,7 @@
       </c>
       <c r="B29" s="32" t="inlineStr">
         <is>
-          <t>298 N8 c/20 por fundação; estribo fechado 55 × 140 cm, C=465 cm.</t>
+          <t>298 N8 c/20 por fundação; estribo fechado 55 × 140 cm, C=465 cm (dimensões internas ao cobrimento de 5 cm da seção de 65 × 150 cm).</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2762,7 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>N13-2 Ø16 C=485 cm na região do rebaixo.</t>
+          <t>N13-2 Ø16 C=485 cm na região do rebaixo. A lista traz 8 un (1 por fundação), enquanto o detalhe chama 2 un — ver aba Validações.</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2802,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -2829,59 +2835,59 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Bitola
 Ø (mm)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Posições</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Compr. total
-(m) - 8x</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Compr. da prancha
+(m)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Massa linear
 (kg/m)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Massa da prancha
 (kg)</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Massa calculada
-(kg)</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Desvio
-(kg)</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Compr. somado
+da lista (m)</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Desvio de
+compr. (m)</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>% da massa</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Barras de 12 m
 (equivalente)</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>Massa por
 fundação (kg)</t>
@@ -2889,7 +2895,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
@@ -2907,10 +2913,10 @@
         <v>4528</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>4528.03</v>
+        <v>11463.36</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H6" s="16" t="n">
         <v>0.14798</v>
@@ -2923,7 +2929,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -2941,10 +2947,10 @@
         <v>10872</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>10872.42</v>
+        <v>6890</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="H7" s="16" t="n">
         <v>0.355321</v>
@@ -2957,7 +2963,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
+      <c r="A8" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -2975,10 +2981,10 @@
         <v>15198</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>15198.45</v>
+        <v>6163.2</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>0.496699</v>
@@ -2996,7 +3002,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
+      <c r="B9" s="12" t="n"/>
       <c r="C9" s="21" t="n">
         <v>24516.56</v>
       </c>
@@ -3005,10 +3011,10 @@
         <v>30599</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>30598.9</v>
+        <v>24516.56</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="22" t="n">
         <v>1</v>
@@ -3023,21 +3029,21 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>- O quadro RESUMO GERAL da prancha fecha exatamente com o somatório da LISTA DE BARRAS nas três bitolas.</t>
+          <t>- As três bitolas fecham exatamente entre a LISTA DE BARRAS e o quadro RESUMO GERAL.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>- TOTAL (kg) impresso na prancha = 30.599 kg. O somatório das massas não arredondadas é 30.598,90 kg; a soma das três linhas já arredondadas é 30.598 kg. A diferença é apenas de arredondamento (menos de 1 kg).</t>
+          <t>- TOTAL (kg) impresso na prancha = 30.599 kg. O somatório não arredondado é 30.598,90 kg; a soma das três linhas já arredondadas é 30.598 kg. A diferença é apenas de arredondamento.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>- A coluna 'Barras de 12 m' é um equivalente de suprimentos (comprimento total / 12 m, arredondado para cima). Não considera perdas de corte, dobra e emendas - ver aba Validações.</t>
+          <t>- A coluna 'Barras de 12 m' é um equivalente de suprimentos (comprimento / 12 m, arredondado para cima). Não considera perdas de corte, dobra e emendas.</t>
         </is>
       </c>
     </row>
@@ -3066,13 +3072,13 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3090,54 +3096,54 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>Massa por posição (N1 a N13), ordenada conforme a prancha. Fonte de dados dos graficos do painel.</t>
+          <t>Massa por posição, na ordem da prancha. Fonte de dados dos gráficos do painel.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Posição</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Bitola
 Ø (mm)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Quant. total
-(8x)</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Quant.
+total</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Compr. total
 (m)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Massa total
 (kg)</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>% da massa</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Função estrutural</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Massa por
 fundação (kg)</t>
@@ -3150,7 +3156,7 @@
           <t>N1</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C6" s="17" t="n">
@@ -3180,7 +3186,7 @@
           <t>N2</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="17" t="n">
@@ -3210,7 +3216,7 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C8" s="17" t="n">
@@ -3240,7 +3246,7 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C9" s="17" t="n">
@@ -3270,7 +3276,7 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C10" s="17" t="n">
@@ -3300,7 +3306,7 @@
           <t>N6</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C11" s="17" t="n">
@@ -3330,7 +3336,7 @@
           <t>N7</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C12" s="17" t="n">
@@ -3360,7 +3366,7 @@
           <t>N8</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C13" s="17" t="n">
@@ -3390,7 +3396,7 @@
           <t>N9</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="17" t="n">
@@ -3420,7 +3426,7 @@
           <t>N10</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C15" s="17" t="n">
@@ -3450,7 +3456,7 @@
           <t>N11</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C16" s="17" t="n">
@@ -3480,7 +3486,7 @@
           <t>N12</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="17" t="n">
@@ -3510,7 +3516,7 @@
           <t>N13</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="17" t="n">
@@ -3540,7 +3546,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
+      <c r="B19" s="12" t="n"/>
       <c r="C19" s="23" t="n">
         <v>2712</v>
       </c>
@@ -3564,35 +3570,34 @@
           <t>AGRUPAMENTO POR FUNÇÃO ESTRUTURAL</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Função estrutural</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Posições</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Quant. total
-(8x)</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Quant. total</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Compr. total
 (m)</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Massa total
 (kg)</t>
@@ -3689,7 +3694,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
+      <c r="B27" s="12" t="n"/>
       <c r="C27" s="23" t="n">
         <v>2712</v>
       </c>
@@ -3737,7 +3742,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>QUANTITATIVO POR TANQUE</t>
+          <t>QUANTITATIVO UNITÁRIO POR FUNDAÇÃO</t>
         </is>
       </c>
     </row>
@@ -3751,51 +3756,51 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>A prancha cobre 8 fundações idênticas (indicação '8x' na planta e na lista de barras). O quantitativo unitário é obtido dividindo os totais por 8.</t>
+          <t>A prancha atende 8 fundações idênticas (indicação '8x' na planta e na lista de barras). O quantitativo unitário é obtido dividindo os totais por 8.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Tanque</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Elemento</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Fundações</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Compr. Ø8
 (m)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Compr. Ø16
 (m)</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Compr. Ø20
 (m)</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Compr. total
 (m)</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Massa de aço
 (kg)</t>
@@ -4048,7 +4053,7 @@
           <t>TOTAL — 8 fundações</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="23" t="n">
         <v>8</v>
       </c>
@@ -4071,46 +4076,46 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>DETALHAMENTO UNITÁRIO - UMA FUNDAÇÃO (VALE PARA CADA UM DOS 8 TANQUES)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+          <t>DETALHAMENTO DE UMA FUNDAÇÃO (VALE PARA CADA UM DOS 8 TANQUES)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Posição</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Bitola
 Ø (mm)</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Quant. por
 fundação</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Compr. unit.
 (cm)</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Compr. por
 fundação (m)</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Massa por
 fundação (kg)</t>
@@ -4123,7 +4128,7 @@
           <t>N1</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C18" s="17" t="n">
@@ -4147,7 +4152,7 @@
           <t>N2</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C19" s="17" t="n">
@@ -4171,7 +4176,7 @@
           <t>N3</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C20" s="17" t="n">
@@ -4195,7 +4200,7 @@
           <t>N4</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="17" t="n">
@@ -4219,7 +4224,7 @@
           <t>N5</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="17" t="n">
@@ -4243,7 +4248,7 @@
           <t>N6</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C23" s="17" t="n">
@@ -4267,7 +4272,7 @@
           <t>N7</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C24" s="17" t="n">
@@ -4291,14 +4296,16 @@
           <t>N8</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C25" s="17" t="n">
         <v>298</v>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>465</v>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
       </c>
       <c r="E25" s="15" t="n">
         <v>1385.7</v>
@@ -4313,14 +4320,16 @@
           <t>N9</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C26" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="14" t="n">
-        <v>473</v>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
       </c>
       <c r="E26" s="15" t="n">
         <v>28.38</v>
@@ -4335,14 +4344,16 @@
           <t>N10</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C27" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="14" t="n">
-        <v>500</v>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="E27" s="15" t="n">
         <v>20</v>
@@ -4357,14 +4368,16 @@
           <t>N11</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="14" t="n">
-        <v>600</v>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="E28" s="15" t="n">
         <v>24</v>
@@ -4379,7 +4392,7 @@
           <t>N12</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C29" s="17" t="n">
@@ -4403,14 +4416,16 @@
           <t>N13</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C30" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>485</v>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
       </c>
       <c r="E30" s="15" t="n">
         <v>4.85</v>
@@ -4425,7 +4440,7 @@
           <t>TOTAL POR FUNDAÇÃO</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
+      <c r="B31" s="12" t="n"/>
       <c r="C31" s="23" t="n">
         <v>339</v>
       </c>
@@ -4458,15 +4473,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="66" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -4491,33 +4506,33 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Escala</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Valor
 (m, m² ou m³)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -4539,11 +4554,7 @@
           <t>1:100</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D6" s="33" t="n"/>
       <c r="E6" s="18" t="inlineStr">
         <is>
           <t>PRANCHA</t>
@@ -4551,7 +4562,7 @@
       </c>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>Planta de armadura do anel de fundação; indicação 298 N8 c.20.</t>
+          <t>Planta de armadura do anel de fundação; indicação 298 N8 c.20 e 6 N9 c.20.</t>
         </is>
       </c>
     </row>
@@ -4571,11 +4582,7 @@
           <t>1:20</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D7" s="33" t="n"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>PRANCHA</t>
@@ -4583,7 +4590,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Seção corrente do anel: 55 cm (radial) × 140 cm (altura); 6 N6 c/20 na face externa e 6 N7 c/20 na face interna.</t>
+          <t>Seção corrente do anel, com 6 N6 c/20 na face externa e 6 N7 c/20 na face interna.</t>
         </is>
       </c>
     </row>
@@ -4603,11 +4610,7 @@
           <t>1:20</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D8" s="33" t="n"/>
       <c r="E8" s="18" t="inlineStr">
         <is>
           <t>PRANCHA</t>
@@ -4615,7 +4618,7 @@
       </c>
       <c r="F8" s="35" t="inlineStr">
         <is>
-          <t>Seção na região do rebaixo, com N10, N11, N13 e 5 N6 / 5 N7 c/20.</t>
+          <t>Seção na região do rebaixo, com 5 N6 / 5 N7 c/20, N10, N11, N8 e 2 N13.</t>
         </is>
       </c>
     </row>
@@ -4635,11 +4638,7 @@
           <t>1:25</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D9" s="33" t="n"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>PRANCHA</t>
@@ -4707,7 +4706,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Desenvolvimento cotado de 5994,2 cm; malha de N1 e N7.</t>
+          <t>Cota impressa de 5994,2 cm. Geometricamente este valor corresponde ao eixo do anel, e não à face interna — ver aba Validações.</t>
         </is>
       </c>
     </row>
@@ -4737,19 +4736,19 @@
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>Desenvolvimento cotado de 5832,7 cm; malha de N1 a N5.</t>
+          <t>Cota impressa de 5832,7 cm. Geometricamente este valor corresponde à face interna — ver aba Validações.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Seção</t>
+          <t>Derivado</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Largura radial da seção corrente</t>
+          <t>Desenvolvimento do eixo do anel (m)</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -4758,28 +4757,28 @@
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>0.55</v>
+        <v>59.941</v>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>PRANCHA</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>Cota 55 cm no CORTE A-A e no CORTE B-B.</t>
+          <t>DERIVADO</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>Média entre os desenvolvimentos das faces externa (61,556 m) e interna (58,327 m). Coincide com a cota de 5994,2 cm impressa na prancha.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Seção</t>
+          <t>Derivado</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Altura da seção corrente</t>
+          <t>Raio do eixo do anel (m)</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -4788,28 +4787,28 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>1.4</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>PRANCHA</t>
+          <t>DERIVADO</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>Cota 140 cm no CORTE A-A.</t>
+          <t>Desenvolvimento do eixo dividido por 2π.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Seção</t>
+          <t>Derivado</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Área da seção corrente (m²)</t>
+          <t>Raio interno do anel (m)</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -4818,28 +4817,28 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>0.77</v>
+        <v>9.215</v>
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
           <t>DERIVADO</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>0,55 m × 1,40 m.</t>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Raio do eixo menos meia largura da seção.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Espaçamento</t>
+          <t>Derivado</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Estribos N8 na seção corrente</t>
+          <t>Raio externo do anel (m)</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
@@ -4848,28 +4847,28 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>0.2</v>
+        <v>9.865</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>PRANCHA</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr">
-        <is>
-          <t>298 N8 c/20 por fundação; 298 × 0,20 m = 59,60 m, coerente com o desenvolvimento da face interna (59,942 m).</t>
+          <t>DERIVADO</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Raio do eixo mais meia largura da seção.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Espaçamento</t>
+          <t>Seção</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Barras horizontais N6 / N7</t>
+          <t>Largura radial da seção (m)</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -4878,28 +4877,28 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>PRANCHA</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>6 N6 c/20 e 6 N7 c/20 no CORTE A-A.</t>
+          <t>DERIVADO</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>A diferença entre os desenvolvimentos das faces externa e interna resulta em 51,4 cm entre as camadas de armadura; somados os 2 × 6,8 cm de cobrimento e meia bitola, a seção é de 65 cm — a mesma das pranchas de formas TX3-059 e 6312 TX3-001. A prancha de formas deste conjunto (DE-5400.00-6310-120-TX3-001) não foi fornecida.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>Traspasse</t>
+          <t>Seção</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Traspasse típico das barras corridas</t>
+          <t>Altura da seção (m)</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -4908,28 +4907,28 @@
         </is>
       </c>
       <c r="D18" s="33" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>PRANCHA</t>
+          <t>DERIVADO</t>
         </is>
       </c>
       <c r="F18" s="35" t="inlineStr">
         <is>
-          <t>Cotas 40 (TIP.) e 160 repetidas nas elevações das faces.</t>
+          <t>O estribo N8 de 55 × 140 cm mais o cobrimento de 5 cm em cada face resulta em 65 × 150 cm, seção idêntica à das pranchas de formas fornecidas.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Espaçamento</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Perímetro médio do anel (m)</t>
+          <t>Estribos N8 na seção corrente (m)</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -4938,28 +4937,28 @@
         </is>
       </c>
       <c r="D19" s="33" t="n">
-        <v>60.749</v>
+        <v>0.2</v>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>DERIVADO</t>
+          <t>PRANCHA</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Média entre os desenvolvimentos das faces externa (61,556 m) e interna (59,942 m).</t>
+          <t>298 N8 c/20 por fundação; 298 × 0,20 = 59,60 m, coerente com o desenvolvimento do eixo (59,94 m).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Espaçamento</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Diâmetro médio implícito (m)</t>
+          <t>Barras horizontais N6 / N7 (m)</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -4968,28 +4967,28 @@
         </is>
       </c>
       <c r="D20" s="33" t="n">
-        <v>19.337</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>DERIVADO</t>
+          <t>PRANCHA</t>
         </is>
       </c>
       <c r="F20" s="35" t="inlineStr">
         <is>
-          <t>Perímetro médio dividido por pi. Valor indicativo — confirmar na prancha de formas.</t>
+          <t>6 N6 c/20 e 6 N7 c/20 no CORTE A-A; 5 + 5 c/20 no CORTE B-B (trecho do rebaixo).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Traspasse</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Volume de concreto por fundação (m³)</t>
+          <t>Traspasse típico das barras corridas (m)</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
@@ -4998,16 +4997,16 @@
         </is>
       </c>
       <c r="D21" s="33" t="n">
-        <v>46.78</v>
+        <v>0.4</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>DERIVADO</t>
+          <t>PRANCHA</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>ESTIMATIVA: área da seção corrente × perímetro médio. Não considera o rebaixo nem variações de seção. O volume oficial deve ser lido na prancha de formas DE-5400.00-6310-120-TX3-001.</t>
+          <t>Cotas 40 (TÍP.) e 160 repetidas nas elevações das faces.</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5018,7 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Volume de concreto — 8 fundações (m³)</t>
+          <t>Área da seção do anel (m²)</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -5028,16 +5027,16 @@
         </is>
       </c>
       <c r="D22" s="33" t="n">
-        <v>374.21</v>
+        <v>0.975</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
           <t>DERIVADO</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
-        <is>
-          <t>ESTIMATIVA - mesma ressalva da linha anterior.</t>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>0,65 m × 1,50 m.</t>
         </is>
       </c>
     </row>
@@ -5049,25 +5048,85 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
+          <t>Volume de concreto por fundação (m³)</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>DERIVADO</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>ESTIMATIVA: área da seção × desenvolvimento do eixo. O mesmo cálculo aplicado ao TQ-6310818 resulta em 52,59 m³ contra os 52,50 m³ declarados na prancha de formas TX3-059 — diferença de 0,17%, o que valida o método. O valor oficial deve sair da prancha de formas deste conjunto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Derivado</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Volume de concreto — 8 fundações (m³)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>467.54</v>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>DERIVADO</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>ESTIMATIVA — mesma ressalva da linha anterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Derivado</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
           <t>Taxa de armadura (kg/m³)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D23" s="33" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="D25" s="33" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>DERIVADO</t>
         </is>
       </c>
-      <c r="F23" s="35" t="inlineStr">
-        <is>
-          <t>ESTIMATIVA: massa total de aço dividida pelo volume estimado. Indicador de aderência; não substitui a prancha de formas.</t>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>Massa de aço por fundação dividida pelo volume estimado. Comparável aos 67,1 kg/m³ do TQ-6310818 e aos 67,3 kg/m³ do TQ-6312824.</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5170,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Dados de carimbo, notas gerais, legenda e documentos vinculados, transcritos da prancha.</t>
@@ -5119,19 +5178,19 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Parâmetro</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Especificação / conteudo transcrito</t>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Especificação / conteúdo transcrito</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5224,7 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>0 - EMISSÃO ORIGINAL - PARA CONSTRUÇÃO (07/08/2026)</t>
+          <t>0 — EMISSÃO ORIGINAL - PARA CONSTRUÇÃO (07/08/2026)</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5236,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Titulo</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
@@ -5233,7 +5292,7 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>Petrobras - SRGE/SI-III (classificação INTERNA)</t>
+          <t>Petrobras — SRGE/SI-III (classificação INTERNA)</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5309,7 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Consorcio TEM Boaventura</t>
+          <t>Consórcio TEM Boaventura</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5343,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Antenor de Castro - CREA 17974D-MG</t>
+          <t>Antenor de Castro — CREA 17974D-MG</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5377,7 @@
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>01 de 01 - A1 (841 × 594 mm) - escala INDICADA</t>
+          <t>01 de 01 — A1 (841 × 594 mm) — escala INDICADA</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5479,7 @@
       </c>
       <c r="C22" s="35" t="inlineStr">
         <is>
-          <t>Ø8 = 0,395 kg/m; Ø16 = 1,578 kg/m; Ø20 = 2,466 kg/m - valores do quadro RESUMO GERAL, coincidentes com os nominais da NBR 7480.</t>
+          <t>Ø8 = 0,395 kg/m; Ø16 = 1,578 kg/m; Ø20 = 2,466 kg/m — valores do quadro RESUMO GERAL, coincidentes com os nominais da NBR 7480.</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5530,7 @@
       </c>
       <c r="C25" s="35" t="inlineStr">
         <is>
-          <t>DE-5400.00-6310-120-TX3-001 - Desenho de fundação - tanques de lubrificação TQ-6310816A/B/C/D &amp; TQ-6310817A/B/C/D - FORMAS.</t>
+          <t>DE-5400.00-6310-120-TX3-001 - Desenho de fundação - tanques de lubrificação TQ-6310816A/B/C/D &amp; TQ-6310817A/B/C/D - FORMAS. Não fornecida nesta análise.</t>
         </is>
       </c>
     </row>
@@ -5527,15 +5586,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="92" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -5552,7 +5611,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Conferência entre o somatório estruturado e os quadros impressos na prancha. Toda divergência está sinalizada de forma explícita.</t>
@@ -5560,32 +5619,32 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Calculado</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Referência</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Desvio</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Critério / observação</t>
         </is>
@@ -5599,7 +5658,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Ø8 - comprimento total (m)</t>
+          <t>Ø8 — comprimento total (m)</t>
         </is>
       </c>
       <c r="C6" s="15" t="n">
@@ -5625,7 +5684,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Ø16 - comprimento total (m)</t>
+          <t>Ø16 — comprimento total (m)</t>
         </is>
       </c>
       <c r="C7" s="15" t="n">
@@ -5651,7 +5710,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Ø20 - comprimento total (m)</t>
+          <t>Ø20 — comprimento total (m)</t>
         </is>
       </c>
       <c r="C8" s="15" t="n">
@@ -5677,7 +5736,7 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Ø8 - massa total (kg)</t>
+          <t>Ø8 — massa total (kg)</t>
         </is>
       </c>
       <c r="C9" s="15" t="n">
@@ -5691,7 +5750,7 @@
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Comprimento × massa linear. Desvio inferior a 0,5 kg, compatível com o arredondamento do quadro.</t>
+          <t>Comprimento do RESUMO GERAL × massa linear. Desvio inferior a 0,5 kg, compatível com o arredondamento do quadro.</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5762,7 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Ø16 - massa total (kg)</t>
+          <t>Ø16 — massa total (kg)</t>
         </is>
       </c>
       <c r="C10" s="15" t="n">
@@ -5717,7 +5776,7 @@
       </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>Comprimento × massa linear. Desvio inferior a 0,5 kg, compatível com o arredondamento do quadro.</t>
+          <t>Comprimento do RESUMO GERAL × massa linear. Desvio inferior a 0,5 kg, compatível com o arredondamento do quadro.</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5788,7 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Ø20 - massa total (kg)</t>
+          <t>Ø20 — massa total (kg)</t>
         </is>
       </c>
       <c r="C11" s="15" t="n">
@@ -5743,7 +5802,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Comprimento × massa linear. Desvio inferior a 0,5 kg, compatível com o arredondamento do quadro.</t>
+          <t>Comprimento do RESUMO GERAL × massa linear. Desvio inferior a 0,5 kg, compatível com o arredondamento do quadro.</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5828,7 @@
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>TOTAL (kg) impresso = 30.599. Somatório não arredondado = 30.598,90 kg. A soma das três linhas já arredondadas resulta 30.598 kg. Diferença exclusivamente de arredondamento.</t>
+          <t>Somatório do quadro RESUMO GERAL contra o TOTAL (kg) impresso na prancha.</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5840,7 @@
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>TOTAL = QUANT. x UNIT. (posições N8, N9, N10, N11, N13)</t>
+          <t>TOTAL = QUANT. × UNIT. (N8, N9, N10, N11, N13)</t>
         </is>
       </c>
       <c r="C13" s="15" t="n">
@@ -5833,7 +5892,7 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>N9 / N10 / N11 / N12 - quantidade total vs. cotas dos detalhes</t>
+          <t>N9 / N10 / N11 / N12 - quantidade vs. cotas dos detalhes</t>
         </is>
       </c>
       <c r="C15" s="15" t="n">
@@ -5847,163 +5906,215 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>N9 = 6/fundação (48/8); N10 = 4 (32/8); N11 = 4 (32/8); N12 = 2x2 = 4 (32/8). Todas coerentes com os detalhes da VISTA C-C.</t>
+          <t>N9 = 6/fundação (48/8); N10 = 4 (32/8); N11 = 4 (32/8); N12 = 2x2 = 4 (32/8). Coerentes com as chamadas da VISTA C-C.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>DIVERGÊNCIA</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>N13 - quantidade por fundação</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="n">
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>N13 - quantidade por fundação (un)</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="38" t="n">
+      <c r="D16" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="38" t="n">
+      <c r="E16" s="37" t="n">
         <v>-1</v>
       </c>
-      <c r="F16" s="39" t="inlineStr">
-        <is>
-          <t>A LISTA DE BARRAS indica QUANT. 8 (1 un por fundação) e TOTAL 38,80 m, internamente consistente. Já o detalhe da VISTA C-C / CORTE B-B chama 'N13-2 Ø16-485' e '2N13', ou seja, 2 un por fundação (16 no total). Se prevalecer o detalhe, acrescem 8 barras, 38,80 m e 61,23 kg de Ø16 (+0,20% da massa total). CONFIRMAR COM O PROJETISTA.</t>
+      <c r="F16" s="38" t="inlineStr">
+        <is>
+          <t>A LISTA DE BARRAS indica QUANT. 8 (1 un por fundação) e TOTAL 38,80 m, internamente consistente. Já o detalhe da VISTA C-C / CORTE B-B chama 'N13-2 Ø16-485' e '2N13', ou seja, 2 un por fundação (16 no total). A prancha irmã TX3-060, de mesma família, traz N13 com 8 un para 4 fundações (2 por fundação), o que reforça a leitura do detalhe. Se prevalecer o detalhe, acrescem 8 barras, 38,80 m e 61,23 kg de Ø16 (+0,20% da massa total). CONFIRMAR COM O PROJETISTA.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>DIVERGÊNCIA</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>N12 - comprimento unitário</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="n">
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>N12 - comprimento unitário implícito (m)</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="n">
         <v>4.71</v>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D17" s="37" t="n">
         <v>1.23</v>
       </c>
-      <c r="E17" s="38" t="n">
+      <c r="E17" s="37" t="n">
         <v>3.48</v>
       </c>
-      <c r="F17" s="39" t="inlineStr">
-        <is>
-          <t>A coluna UNIT. traz 'VAR' e a forma está cotada com perna variável (113 a 133) cm. Contudo, TOTAL 150,72 m para 32 un implica comprimento médio de 471 cm por barra - próximo dos estribos N8 (465) e N9 (473) e não da faixa cotada. O RESUMO GERAL adota 150,72 m. Se o comprimento médio fosse 123 cm, o total cairia para 39,36 m (-43,99 kg, -0,14% da massa total). CONFIRMAR COM O PROJETISTA.</t>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>A coluna UNIT. traz 'VAR' e a forma está cotada com perna variável (113 a 133) cm. Contudo, TOTAL 150,72 m para 32 un implica comprimento médio de 471 cm por barra - próximo dos estribos N8 (465) e N9 (473) e não da faixa cotada. O mesmo padrão aparece nas outras duas pranchas de armadura da série (483 cm em ambas). CONFIRMAR COM O PROJETISTA.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Coerência geométrica</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>Estribos N8 x desenvolvimento do anel (m)</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="D18" s="15" t="n">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>DIVERGÊNCIA</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>Cotas das elevações FACE INTERNA e FACE SUP./INF. (m)</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="n">
         <v>59.942</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="F18" s="35" t="inlineStr">
-        <is>
-          <t>298 estribos a cada 20 cm cobrem 59,60 m, praticamente o desenvolvimento cotado da face interna (59,942 m). Distribuição coerente.</t>
+      <c r="D18" s="37" t="n">
+        <v>58.327</v>
+      </c>
+      <c r="E18" s="37" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="F18" s="38" t="inlineStr">
+        <is>
+          <t>A cota do eixo do anel tem de ser a média das cotas das faces externa e interna. Aqui, (61,556 + 58,327)/2 = 59,942 m — exatamente o valor impresso na FACE INTERNA - ELEVAÇÃO, e não na FACE SUPERIOR E INFERIOR - PLANTA, que é a vista desenvolvida no eixo. Nas pranchas irmãs TX3-060 e 6312 TX3-002 a convenção é a inversa e fecha corretamente. Os dois valores parecem trocados entre as vistas. Não altera o quantitativo de aço; afeta a leitura da geometria.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Materiais</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Massas lineares adotadas (kg/m)</t>
+          <t>Coerência geométrica</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Estribos N8 × desenvolvimento do eixo (m)</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>3</v>
+        <v>59.6</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>3</v>
+        <v>59.94</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Ø8 = 0,395; Ø16 = 1,578; Ø20 = 2,466. Coincidem com os valores nominais da NBR 7480 para aço CA-50.</t>
+          <t>298 estribos a cada 20 cm cobrem 59,60 m, contra 59,94 m de desenvolvimento do eixo. Distribuição coerente.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>Escopo</t>
+          <t>Coerência entre pranchas</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Perdas de corte, dobra e emendas</t>
+          <t>Seção do anel (m)</t>
         </is>
       </c>
       <c r="C20" s="15" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="35" t="inlineStr">
         <is>
-          <t>Os quantitativos são os do desenho (comprimentos de projeto). Não há acréscimo de perdas. Para suprimentos, aplicar a taxa de perda contratual sobre a massa por bitola.</t>
+          <t>A diferença entre as cotas das faces externa e interna (61,556 - 58,327 = 3,229 m) corresponde a 51,4 cm de afastamento radial entre as camadas de armadura; somado o cobrimento, resulta em 65 cm — exatamente a seção das pranchas de formas TX3-059 e 6312 TX3-001. Atenção: o 55 × 140 cm do CORTE A-A é a dimensão do ESTRIBO, não da seção de concreto.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>Escopo</t>
+          <t>Materiais</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Concreto, formas e chumbadores</t>
+          <t>Massas lineares adotadas (kg/m)</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Esta prancha é exclusivamente de ARMADURAS. Volume de concreto, formas e insertos devem ser lidos na prancha de formas DE-5400.00-6310-120-TX3-001 (documento complementar), não fornecida nesta análise.</t>
+          <t>Ø8 = 0,395; Ø16 = 1,578; Ø20 = 2,466. Coincidem com os valores nominais da NBR 7480 para aço CA-50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Perdas de corte, dobra e emendas</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Os quantitativos são os do desenho (comprimentos de projeto). Não há acréscimo de perdas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Concreto, formas e terraplenagem</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Esta prancha é exclusivamente de ARMADURAS. O volume de concreto informado na aba Geometria é ESTIMATIVA: a prancha de formas deste conjunto (DE-5400.00-6310-120-TX3-001) não foi fornecida.</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6047,14 +6158,14 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Tópico</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Conteudo</t>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Conteúdo</t>
         </is>
       </c>
     </row>
@@ -6090,91 +6201,115 @@
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>A prancha atende 8 fundações idênticas - indicação '8x' no titulo da planta e no titulo da lista de barras. As colunas QUANT. e TOTAL do desenho já são o somatório das 8 fundações; os valores unitários das abas são derivados por divisão por 8. Essa leitura foi confirmada pela cota '298 N8 c.20' da planta (298 × 8 = 2.384, exatamente a quantidade da lista).</t>
+          <t>A prancha atende 8 fundações idênticas - indicação '8x' no título da planta e da lista de barras. As colunas QUANT. e TOTAL do desenho já são o somatório das 8 fundações. A leitura foi confirmada pela cota '298 N8 c.20' da planta (298 × 8 = 2.384, exatamente a quantidade da lista).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>Como usar</t>
+          <t>Seção do anel</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Comece pelo Dashboard Executivo para a leitura gerencial. Para auditoria, use Lista de Barras (transcrição integral), Resumo por Bitola (fechamento contra o quadro do desenho), Resumo por Posição e Quantitativo por Tanque. As abas Geometria e Seções e Parâmetros Técnicos guardam as cotas e o carimbo.</t>
+          <t>A seção de concreto é de 65 × 150 cm. O 55 × 140 cm que aparece no CORTE A-A é a dimensão do ESTRIBO N8, medida dentro do cobrimento de 5 cm. A leitura foi confirmada pelas pranchas de formas TX3-059 e 6312 TX3-001, que cotam 65 × 150 cm, e pelo afastamento radial entre as camadas de armadura desta prancha.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>Critério de massa</t>
+          <t>Volume de concreto</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Massa = comprimento total × massa linear nominal (Ø8 = 0,395 kg/m; Ø16 = 1,578 kg/m; Ø20 = 2,466 kg/m), exatamente como no quadro RESUMO GERAL da prancha e em linha com a NBR 7480.</t>
+          <t>A prancha de formas deste conjunto (DE-5400.00-6310-120-TX3-001) não foi fornecida, de modo que o volume de concreto na aba Geometria e Seções é ESTIMATIVA. O método foi validado no TQ-6310818: seção × desenvolvimento do eixo resulta em 52,59 m³ contra os 52,50 m³ declarados na prancha de formas TX3-059 (0,17% de diferença).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>Valores DERIVADOS</t>
+          <t>Controle crítico</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Na aba Geometria e Seções, as linhas marcadas como DERIVADO (perímetro médio, diâmetro implícito, volume de concreto e taxa de armadura) NÃO constam do desenho: são cálculo próprio, apenas indicativo. O volume oficial de concreto deve sair da prancha de formas DE-5400.00-6310-120-TX3-001, que não foi fornecida.</t>
+          <t>Três divergências do próprio desenho estão destacadas na aba Validações: (1) N13 - a lista traz 8 un (1/fundação) enquanto o detalhe chama 2, leitura reforçada pela prancha irmã TX3-060 (+61,23 kg); (2) N12 - forma cotada em (113 a 133) cm, mas o total implica 471 cm por barra; (3) as cotas de desenvolvimento das vistas FACE INTERNA e FACE SUPERIOR E INFERIOR parecem trocadas entre si. Confirmar com o projetista antes da compra.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>Controle crítico</t>
+          <t>Como usar</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Duas divergências do próprio desenho estão destacadas na aba Validações: (1) N13 - a lista traz 8 un (1 por fundação) enquanto o detalhe chama 'N13-2', o que daria 16 un (+61,23 kg); (2) N12 — a forma está cotada com perna variável (113 a 133) cm, mas o TOTAL de 150,72 m para 32 un implica comprimento médio de 471 cm. Ambas devem ser confirmadas com o projetista antes da compra.</t>
+          <t>Comece pelo Dashboard Executivo. Para auditoria, use Lista de Barras (transcrição integral), Resumo por Bitola, Resumo por Posição e Quantitativo Unitário. Geometria e Seções e Parâmetros Técnicos guardam as cotas e o carimbo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Perdas</t>
+          <t>Critério de massa</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Os números são os de projeto. Nenhuma taxa de perda de corte, dobra ou emenda foi acrescida. A coluna 'Barras de 12 m' e apenas um equivalente de suprimento (comprimento / 12 m, arredondado para cima).</t>
+          <t>Massa = comprimento total × massa linear nominal (Ø8 = 0,395 kg/m; Ø16 = 1,578 kg/m; Ø20 = 2,466 kg/m), exatamente como no quadro RESUMO GERAL da prancha e em linha com a NBR 7480.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>Unidades</t>
+          <t>Valores DERIVADOS</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>mm = milímetro (bitola); cm = centímetro (cotas do desenho); m = metro; kg = quilograma; t = tonelada; un = unidade; CORR = barra corrida; VAR = comprimento variável.</t>
+          <t>Na aba Geometria e Seções, as linhas marcadas como DERIVADO não constam do desenho: são cálculo próprio, apenas indicativo, para apoio de planejamento.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
+          <t>Perdas</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Os números são os de projeto. Nenhuma taxa de perda de corte, dobra ou emenda foi acrescida. A coluna 'Barras de 12 m' é apenas um equivalente de suprimento (comprimento / 12 m, arredondado para cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>mm = milímetro (bitola); cm = centímetro (cotas do desenho); m = metro; kg = quilograma; t = tonelada; un = unidade; CORR = barra corrida; VAR = comprimento variável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
           <t>Limite de uso</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Levantamento para planejamento, orçamento e controle. Qualquer uso para execução ou compra deve ser submetido a validação do responsável técnico do projeto.</t>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Levantamento para planejamento, orçamento e controle. Qualquer uso para execução ou compra deve ser submetido à validação do responsável técnico do projeto.</t>
         </is>
       </c>
     </row>
